--- a/inputs/templates/TEMPLATE_FONDO_ALTO_APORTE.xlsx
+++ b/inputs/templates/TEMPLATE_FONDO_ALTO_APORTE.xlsx
@@ -2391,11 +2391,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="63917377"/>
-        <c:axId val="56438818"/>
+        <c:axId val="8876388"/>
+        <c:axId val="27652768"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="63917377"/>
+        <c:axId val="8876388"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="43373"/>
@@ -2429,7 +2429,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="56438818"/>
+        <c:crossAx val="27652768"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
@@ -2441,7 +2441,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="56438818"/>
+        <c:axId val="27652768"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="100"/>
@@ -2484,7 +2484,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="63917377"/>
+        <c:crossAx val="8876388"/>
         <c:crossesAt val="38687"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3237,7 +3237,7 @@
                   <c:v>138.390428484755</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>103.189043644737</c:v>
+                  <c:v>104.668455958127</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4564,11 +4564,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="42798722"/>
-        <c:axId val="58794859"/>
+        <c:axId val="22210765"/>
+        <c:axId val="8186561"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="42798722"/>
+        <c:axId val="22210765"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4600,7 +4600,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="58794859"/>
+        <c:crossAx val="8186561"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
@@ -4611,7 +4611,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="58794859"/>
+        <c:axId val="8186561"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="8"/>
@@ -4688,7 +4688,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="42798722"/>
+        <c:crossAx val="22210765"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -8673,7 +8673,7 @@
       </c>
       <c r="AW20" s="32" t="n">
         <f aca="false">LOOKUP(AW19,$A$3:$A$2971,$B$3:$B$2971)</f>
-        <v>19635.3400812264</v>
+        <v>19916.8502383877</v>
       </c>
       <c r="AX20" s="32" t="n">
         <f aca="false">LOOKUP(AX19,$A$3:$A$2971,$B$3:$B$2971)</f>
@@ -8928,7 +8928,7 @@
       </c>
       <c r="AH22" s="21" t="n">
         <f aca="false">+S23/R23-1</f>
-        <v>-0.254362857499898</v>
+        <v>-0.243672722859896</v>
       </c>
       <c r="AI22" s="21"/>
       <c r="AJ22" s="21"/>
@@ -8940,7 +8940,7 @@
       <c r="AP22" s="21"/>
       <c r="AQ22" s="22" t="n">
         <f aca="false">+(S23/P23-1)/COUNTA(AE22:AP22)*12</f>
-        <v>-0.746250693705866</v>
+        <v>-0.71393888658704</v>
       </c>
       <c r="AR22" s="8"/>
       <c r="AS22" s="8"/>
@@ -9003,7 +9003,7 @@
       </c>
       <c r="S23" s="18" t="n">
         <f aca="false">+B247</f>
-        <v>19635.3400812264</v>
+        <v>19916.8502383877</v>
       </c>
       <c r="Y23" s="18"/>
       <c r="AD23" s="25" t="s">
@@ -9495,23 +9495,23 @@
       </c>
       <c r="AX29" s="42" t="n">
         <f aca="false">$AW20/AX20-1</f>
-        <v>-0.254362857499898</v>
+        <v>-0.243672722859896</v>
       </c>
       <c r="AY29" s="42" t="n">
         <f aca="false">$AW20/AY20-1</f>
-        <v>-0.248750231235289</v>
+        <v>-0.237979628862347</v>
       </c>
       <c r="AZ29" s="42" t="n">
         <f aca="false">$AW20/AZ20-1</f>
-        <v>-0.239809516977627</v>
+        <v>-0.228910732364632</v>
       </c>
       <c r="BA29" s="42" t="n">
         <f aca="false">$AW20/BA20-1</f>
-        <v>-0.220741912237796</v>
+        <v>-0.209569757039683</v>
       </c>
       <c r="BB29" s="42" t="n">
         <f aca="false">+AQ88</f>
-        <v>-0.746250693705866</v>
+        <v>-0.71393888658704</v>
       </c>
       <c r="BC29" s="43"/>
       <c r="BD29" s="26"/>
@@ -14729,7 +14729,7 @@
       </c>
       <c r="AH88" s="59" t="n">
         <f aca="false">+AH22</f>
-        <v>-0.254362857499898</v>
+        <v>-0.243672722859896</v>
       </c>
       <c r="AI88" s="59"/>
       <c r="AJ88" s="59"/>
@@ -14741,7 +14741,7 @@
       <c r="AP88" s="59"/>
       <c r="AQ88" s="59" t="n">
         <f aca="false">+AQ22</f>
-        <v>-0.746250693705866</v>
+        <v>-0.71393888658704</v>
       </c>
     </row>
     <row r="89" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21106,15 +21106,15 @@
         <v>46142</v>
       </c>
       <c r="B247" s="72" t="n">
-        <v>19635.3400812264</v>
+        <v>19916.8502383877</v>
       </c>
       <c r="C247" s="24" t="n">
         <f aca="false">(B247/B246-1)/(A247-A246)*30</f>
-        <v>-0.254362857499898</v>
+        <v>-0.243672722859896</v>
       </c>
       <c r="D247" s="18" t="n">
         <f aca="false">+D246*(1+C247)</f>
-        <v>103.189043644737</v>
+        <v>104.668455958127</v>
       </c>
       <c r="F247" s="16" t="n">
         <v>46142</v>
@@ -21201,23 +21201,23 @@
       </c>
       <c r="T2" s="79" t="n">
         <f aca="false">+'Datos ICP (2)'!AX29</f>
-        <v>-0.254362857499898</v>
+        <v>-0.243672722859896</v>
       </c>
       <c r="U2" s="79" t="n">
         <f aca="false">+'Datos ICP (2)'!AY29</f>
-        <v>-0.248750231235289</v>
+        <v>-0.237979628862347</v>
       </c>
       <c r="V2" s="79" t="n">
         <f aca="false">+'Datos ICP (2)'!AZ29</f>
-        <v>-0.239809516977627</v>
+        <v>-0.228910732364632</v>
       </c>
       <c r="W2" s="79" t="n">
         <f aca="false">+'Datos ICP (2)'!BA29</f>
-        <v>-0.220741912237796</v>
+        <v>-0.209569757039683</v>
       </c>
       <c r="X2" s="79" t="n">
         <f aca="false">+'Datos ICP (2)'!BB29</f>
-        <v>-0.746250693705866</v>
+        <v>-0.71393888658704</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22965,7 +22965,7 @@
       </c>
       <c r="H39" s="93" t="n">
         <f aca="false">+'Datos ICP (2)'!AH88</f>
-        <v>-0.254362857499898</v>
+        <v>-0.243672722859896</v>
       </c>
       <c r="I39" s="93"/>
       <c r="J39" s="93"/>
@@ -22977,7 +22977,7 @@
       <c r="P39" s="93"/>
       <c r="Q39" s="92" t="n">
         <f aca="false">+'Datos ICP (2)'!AQ88</f>
-        <v>-0.746250693705866</v>
+        <v>-0.71393888658704</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/inputs/templates/TEMPLATE_FONDO_ALTO_APORTE.xlsx
+++ b/inputs/templates/TEMPLATE_FONDO_ALTO_APORTE.xlsx
@@ -2391,11 +2391,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="8876388"/>
-        <c:axId val="27652768"/>
+        <c:axId val="74639277"/>
+        <c:axId val="55303404"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="8876388"/>
+        <c:axId val="74639277"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="43373"/>
@@ -2429,7 +2429,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="27652768"/>
+        <c:crossAx val="55303404"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
@@ -2441,7 +2441,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="27652768"/>
+        <c:axId val="55303404"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="100"/>
@@ -2484,7 +2484,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="8876388"/>
+        <c:crossAx val="74639277"/>
         <c:crossesAt val="38687"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4564,11 +4564,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="22210765"/>
-        <c:axId val="8186561"/>
+        <c:axId val="12828649"/>
+        <c:axId val="67424104"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="22210765"/>
+        <c:axId val="12828649"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4600,7 +4600,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="8186561"/>
+        <c:crossAx val="67424104"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
@@ -4611,7 +4611,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="8186561"/>
+        <c:axId val="67424104"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="8"/>
@@ -4688,7 +4688,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="22210765"/>
+        <c:crossAx val="12828649"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>

--- a/inputs/templates/TEMPLATE_FONDO_ALTO_APORTE.xlsx
+++ b/inputs/templates/TEMPLATE_FONDO_ALTO_APORTE.xlsx
@@ -2391,11 +2391,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="74639277"/>
-        <c:axId val="55303404"/>
+        <c:axId val="69450109"/>
+        <c:axId val="44771925"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="74639277"/>
+        <c:axId val="69450109"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="43373"/>
@@ -2429,7 +2429,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="55303404"/>
+        <c:crossAx val="44771925"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
@@ -2441,7 +2441,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="55303404"/>
+        <c:axId val="44771925"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="100"/>
@@ -2484,7 +2484,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="74639277"/>
+        <c:crossAx val="69450109"/>
         <c:crossesAt val="38687"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4564,11 +4564,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="12828649"/>
-        <c:axId val="67424104"/>
+        <c:axId val="28243539"/>
+        <c:axId val="29775806"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="12828649"/>
+        <c:axId val="28243539"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4600,7 +4600,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="67424104"/>
+        <c:crossAx val="29775806"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
@@ -4611,7 +4611,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="67424104"/>
+        <c:axId val="29775806"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="8"/>
@@ -4688,7 +4688,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="12828649"/>
+        <c:crossAx val="28243539"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>

--- a/inputs/templates/TEMPLATE_FONDO_ALTO_APORTE.xlsx
+++ b/inputs/templates/TEMPLATE_FONDO_ALTO_APORTE.xlsx
@@ -2391,11 +2391,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="69450109"/>
-        <c:axId val="44771925"/>
+        <c:axId val="54314586"/>
+        <c:axId val="20621983"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="69450109"/>
+        <c:axId val="54314586"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="43373"/>
@@ -2429,7 +2429,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="44771925"/>
+        <c:crossAx val="20621983"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
@@ -2441,7 +2441,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="44771925"/>
+        <c:axId val="20621983"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="100"/>
@@ -2484,7 +2484,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="69450109"/>
+        <c:crossAx val="54314586"/>
         <c:crossesAt val="38687"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4564,11 +4564,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="28243539"/>
-        <c:axId val="29775806"/>
+        <c:axId val="3085085"/>
+        <c:axId val="36278935"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="28243539"/>
+        <c:axId val="3085085"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4600,7 +4600,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="29775806"/>
+        <c:crossAx val="36278935"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
@@ -4611,7 +4611,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="29775806"/>
+        <c:axId val="36278935"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="8"/>
@@ -4688,7 +4688,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="28243539"/>
+        <c:crossAx val="3085085"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
